--- a/files/港岛-香港仔及鸭脷洲-逸南.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-逸南.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逸南 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1005,7 +869,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1251,7 +1115,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1543,7 +1407,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1835,7 +1699,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1881,7 +1745,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1973,7 +1837,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2065,7 +1929,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2111,7 +1975,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2349,7 +2213,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-21</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2395,7 +2259,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2441,7 +2305,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2487,7 +2351,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2625,7 +2489,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2671,7 +2535,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2717,7 +2581,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2901,7 +2765,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2947,7 +2811,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2993,7 +2857,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3039,7 +2903,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3131,7 +2995,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3177,7 +3041,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3223,7 +3087,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3269,7 +3133,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3315,7 +3179,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3453,7 +3317,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-19</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3499,7 +3363,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3545,7 +3409,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3741,7 +3605,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3787,7 +3651,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3833,7 +3697,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3925,7 +3789,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3971,7 +3835,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -4017,7 +3881,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -4063,7 +3927,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4155,7 +4019,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4201,7 +4065,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4247,7 +4111,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-28</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4293,7 +4157,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4339,7 +4203,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4385,7 +4249,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4431,7 +4295,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4477,7 +4341,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4523,7 +4387,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4569,7 +4433,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4615,7 +4479,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4661,7 +4525,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4707,7 +4571,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4753,7 +4617,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-27</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4799,7 +4663,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4845,7 +4709,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-08</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4891,7 +4755,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4937,7 +4801,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -5029,7 +4893,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5075,7 +4939,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5121,7 +4985,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5167,7 +5031,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5213,7 +5077,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5259,7 +5123,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5305,7 +5169,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-27</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5351,7 +5215,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5443,7 +5307,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5489,7 +5353,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5627,7 +5491,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5673,7 +5537,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-19</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5719,7 +5583,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5765,7 +5629,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5949,7 +5813,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-25</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5995,7 +5859,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -6041,7 +5905,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6087,7 +5951,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6133,7 +5997,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6179,7 +6043,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6225,7 +6089,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6271,7 +6135,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6317,7 +6181,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6363,7 +6227,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6409,7 +6273,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6455,7 +6319,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6551,7 +6415,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6597,7 +6461,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6643,7 +6507,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6689,7 +6553,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6735,7 +6599,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6827,7 +6691,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6873,7 +6737,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6965,7 +6829,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -7011,7 +6875,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7057,7 +6921,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7103,7 +6967,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7125,1417 +6989,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>逸南 - 逸南 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>138 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>91 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>23 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>24 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 183呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 264呎 (1房)
-$736万
-$27,897/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 264呎 (1房)
-$716万
-$27,125/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 264呎 (1房)
-$726万
-$27,506/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>F | 264呎 (1房)
-$749万
-$28,383/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 264呎 (1房)
-$720万
-$27,274/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
-        <is>
-          <t>F | 264呎 (1房)
-$741万
-$28,068/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 264呎 (1房)
-$714万
-$27,039/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$515万
-$27,700/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$529万
-$28,929/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$492万
-$26,910/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$530万
-$28,505/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 264呎 (1房)
-$672万
-$25,451/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 264呎 (1房)
-$708万
-$26,808/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$512万
-$27,538/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$527万
-$28,344/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>F | 264呎 (1房)
-$726万
-$27,519/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 264呎 (1房)
-$704万
-$26,655/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$509万
-$27,381/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$524万
-$28,607/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$518万
-$28,301/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$493万
-$26,492/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 264呎 (1房)
-$662万
-$25,092/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 264呎 (1房)
-$707万
-$26,780/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$539万
-$28,957/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$520万
-$28,443/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$515万
-$28,137/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$521万
-$28,016/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 264呎 (1房)
-$666万
-$25,215/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 264呎 (1房)
-$678万
-$25,700/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$530万
-$28,497/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$486万
-$26,582/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$512万
-$27,978/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$487万
-$26,184/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 264呎 (1房)
-$655万
-$24,803/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 264呎 (1房)
-$728万
-$27,585/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$506万
-$27,182/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$514万
-$28,115/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$509万
-$27,814/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$484万
-$26,037/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 264呎 (1房)
-$675万
-$25,567/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 264呎 (1房)
-$687万
-$26,035/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$497万
-$26,734/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 264呎 (1房)
-$655万
-$24,808/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 264呎 (1房)
-$666万
-$25,245/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$500万
-$26,855/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$504万
-$27,514/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$473万
-$25,837/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$509万
-$27,376/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 264呎 (1房)
-$667万
-$25,279/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 264呎 (1房)
-$698万
-$26,426/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$523万
-$28,097/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$506万
-$27,628/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$470万
-$25,683/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$476万
-$25,582/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="19" t="inlineStr">
-        <is>
-          <t>F | 264呎 (1房)
-$705万
-$26,716/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 242呎 (1房)
-$663万
-$27,401/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$493万
-$26,528/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$477万
-$26,091/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$467万
-$25,534/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$473万
-$25,431/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 242呎 (1房)
-$652万
-$26,930/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 242呎 (1房)
-$636万
-$26,281/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$485万
-$26,088/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$470万
-$25,663/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$464万
-$25,380/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$468万
-$25,153/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 242呎 (1房)
-$647万
-$26,755/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 242呎 (1房)
-$639万
-$26,396/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$481万
-$25,845/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$470万
-$25,707/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$485万
-$26,487/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$500万
-$26,866/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 242呎 (1房)
-$611万
-$25,236/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 242呎 (1房)
-$626万
-$25,869/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$475万
-$25,522/呎
-(21年-06月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$465万
-$25,396/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$479万
-$26,167/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$461万
-$24,779/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 242呎 (1房)
-$639万
-$26,407/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 242呎 (1房)
-$638万
-$26,347/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$470万
-$25,284/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$456万
-$24,897/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$479万
-$26,186/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$492万
-$26,462/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 242呎 (1房)
-$635万
-$26,231/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 242呎 (1房)
-$636万
-$26,262/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$494万
-$26,544/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$483万
-$26,404/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$478万
-$26,104/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$486万
-$26,134/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 242呎 (1房)
-$601万
-$24,825/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 242呎 (1房)
-$623万
-$25,729/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$471万
-$25,308/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$451万
-$24,671/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$451万
-$24,643/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$450万
-$24,215/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 242呎 (1房)
-$596万
-$24,642/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 242呎 (1房)
-$612万
-$25,291/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$473万
-$25,821/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$443万
-$24,235/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$464万
-$24,963/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 242呎 (1房)
-$592万
-$24,479/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 242呎 (1房)
-$612万
-$25,305/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$488万
-$26,210/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$444万
-$24,286/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$439万
-$24,003/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$444万
-$23,857/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 242呎 (1房)
-$593万
-$24,488/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 242呎 (1房)
-$600万
-$24,786/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 186呎 (开放式)
-$452万
-$24,314/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 183呎 (开放式)
-$439万
-$23,983/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 183呎 (开放式)
-$438万
-$23,947/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 186呎 (开放式)
-$428万
-$22,990/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>F | 242呎 (1房)
-$581万
-$23,997/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-逸南.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-逸南.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逸南" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +142,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +223,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6989,4 +7168,1417 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>逸南 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 183呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 264呎 (1房)
+$736万
+$27,897/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 264呎 (1房)
+$716万
+$27,125/呎
+(23年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 264呎 (1房)
+$726万
+$27,506/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>F | 264呎 (1房)
+$749万
+$28,383/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 264呎 (1房)
+$720万
+$27,274/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>F | 264呎 (1房)
+$741万
+$28,068/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 264呎 (1房)
+$714万
+$27,039/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$515万
+$27,700/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$529万
+$28,929/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$492万
+$26,910/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$530万
+$28,505/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 264呎 (1房)
+$672万
+$25,451/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 264呎 (1房)
+$708万
+$26,808/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$512万
+$27,538/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$527万
+$28,344/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>F | 264呎 (1房)
+$726万
+$27,519/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 264呎 (1房)
+$704万
+$26,655/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$509万
+$27,381/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$524万
+$28,607/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$518万
+$28,301/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$493万
+$26,492/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 264呎 (1房)
+$662万
+$25,092/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 264呎 (1房)
+$707万
+$26,780/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$539万
+$28,957/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$520万
+$28,443/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$515万
+$28,137/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$521万
+$28,016/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 264呎 (1房)
+$666万
+$25,215/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 264呎 (1房)
+$678万
+$25,700/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$530万
+$28,497/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$486万
+$26,582/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$512万
+$27,978/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$487万
+$26,184/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 264呎 (1房)
+$655万
+$24,803/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 264呎 (1房)
+$728万
+$27,585/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$506万
+$27,182/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$514万
+$28,115/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$509万
+$27,814/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$484万
+$26,037/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 264呎 (1房)
+$675万
+$25,567/呎
+(21年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 264呎 (1房)
+$687万
+$26,035/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$497万
+$26,734/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 264呎 (1房)
+$655万
+$24,808/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 264呎 (1房)
+$666万
+$25,245/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$500万
+$26,855/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$504万
+$27,514/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$473万
+$25,837/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$509万
+$27,376/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 264呎 (1房)
+$667万
+$25,279/呎
+(21年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 264呎 (1房)
+$698万
+$26,426/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$523万
+$28,097/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$506万
+$27,628/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$470万
+$25,683/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$476万
+$25,582/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>F | 264呎 (1房)
+$705万
+$26,716/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 242呎 (1房)
+$663万
+$27,401/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$493万
+$26,528/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$477万
+$26,091/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$467万
+$25,534/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$473万
+$25,431/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 242呎 (1房)
+$652万
+$26,930/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 242呎 (1房)
+$636万
+$26,281/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$485万
+$26,088/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$470万
+$25,663/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$464万
+$25,380/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$468万
+$25,153/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 242呎 (1房)
+$647万
+$26,755/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 242呎 (1房)
+$639万
+$26,396/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$481万
+$25,845/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$470万
+$25,707/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$485万
+$26,487/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$500万
+$26,866/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 242呎 (1房)
+$611万
+$25,236/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 242呎 (1房)
+$626万
+$25,869/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$475万
+$25,522/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$465万
+$25,396/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$479万
+$26,167/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$461万
+$24,779/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 242呎 (1房)
+$639万
+$26,407/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 242呎 (1房)
+$638万
+$26,347/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$470万
+$25,284/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$456万
+$24,897/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$479万
+$26,186/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$492万
+$26,462/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 242呎 (1房)
+$635万
+$26,231/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 242呎 (1房)
+$636万
+$26,262/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$494万
+$26,544/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$483万
+$26,404/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$478万
+$26,104/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$486万
+$26,134/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 242呎 (1房)
+$601万
+$24,825/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 242呎 (1房)
+$623万
+$25,729/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$471万
+$25,308/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$451万
+$24,671/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$451万
+$24,643/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$450万
+$24,215/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 242呎 (1房)
+$596万
+$24,642/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 242呎 (1房)
+$612万
+$25,291/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$473万
+$25,821/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$443万
+$24,235/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$464万
+$24,963/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 242呎 (1房)
+$592万
+$24,479/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 242呎 (1房)
+$612万
+$25,305/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$488万
+$26,210/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$444万
+$24,286/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$439万
+$24,003/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$444万
+$23,857/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 242呎 (1房)
+$593万
+$24,488/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 242呎 (1房)
+$600万
+$24,786/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 186呎 (开放式)
+$452万
+$24,314/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 183呎 (开放式)
+$439万
+$23,983/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 183呎 (开放式)
+$438万
+$23,947/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 186呎 (开放式)
+$428万
+$22,990/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 242呎 (1房)
+$581万
+$23,997/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-逸南.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-逸南.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J140"/>
+  <dimension ref="A1:N140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,10 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -713,6 +717,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -763,6 +787,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -813,6 +857,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -863,6 +927,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -913,6 +997,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -963,6 +1067,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1013,6 +1137,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1059,6 +1203,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>7160900</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>27125</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1109,6 +1269,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1159,6 +1339,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1209,6 +1409,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1259,6 +1479,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1305,6 +1545,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>7364900</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>27897</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1351,6 +1607,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>7043420</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>26680</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1401,6 +1673,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1451,6 +1743,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1501,6 +1813,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1551,6 +1883,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1597,6 +1949,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>7261500</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>27506</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1643,6 +2011,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>6965400</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>26384</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1693,6 +2077,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1743,6 +2147,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1793,6 +2217,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1843,6 +2287,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1889,6 +2353,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>7200400</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>27274</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1935,6 +2415,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>6719120</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>25451</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1981,6 +2477,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>4983880</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>26795</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2027,6 +2539,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>4924600</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>26910</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2073,6 +2601,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>4976360</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>27193</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2119,6 +2663,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>5152140</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>27700</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2165,6 +2725,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>7138360</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>27039</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2211,6 +2787,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>6829100</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>25868</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2257,6 +2849,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>4955680</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>26643</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2307,6 +2915,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2357,6 +2985,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2403,6 +3051,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>5122060</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>27538</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2449,6 +3113,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>7077260</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>26808</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2495,6 +3175,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>6624180</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>25092</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2541,6 +3237,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>4927480</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>26492</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2587,6 +3299,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>4868260</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>26603</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2633,6 +3361,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>4920900</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>26890</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2679,6 +3423,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>5092920</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>27381</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2725,6 +3485,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>7036840</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>26655</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2771,6 +3547,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>6656650</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>25215</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2817,6 +3609,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>4898340</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>26335</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2863,6 +3671,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>4840060</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>26448</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2909,6 +3733,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>4892700</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>26736</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2955,6 +3795,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>5386000</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>28957</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3001,6 +3857,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>7069900</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>26780</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3047,6 +3919,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>6548040</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>24803</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3093,6 +3981,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>4870140</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>26184</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3139,6 +4043,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>4812800</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>26299</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3185,6 +4105,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>4864500</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>26582</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3231,6 +4167,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>5300460</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>28497</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3277,6 +4229,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>6784920</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>25700</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3323,6 +4291,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>6749750</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>25567</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3369,6 +4353,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>4842880</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>26037</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3415,6 +4415,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>4784600</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>26145</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3461,6 +4477,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>4836300</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>26428</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3507,6 +4539,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>5055900</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>27182</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3553,6 +4601,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>7282440</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>27585</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3599,6 +4663,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>6549300</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>24808</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3649,6 +4729,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3699,6 +4799,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3749,6 +4869,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3795,6 +4935,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>4972600</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>26734</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3841,6 +4997,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>6873280</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>26035</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3887,6 +5059,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>6673750</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>25279</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3933,6 +5121,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>4786480</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>25734</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3979,6 +5183,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>4728200</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>25837</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4025,6 +5245,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>5035140</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>27514</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4071,6 +5307,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>4995100</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>26855</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4117,6 +5369,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>6664600</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>25245</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4163,6 +5431,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>6629820</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>25113</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4209,6 +5493,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>4758280</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>25582</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4255,6 +5555,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>4700000</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>25683</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4301,6 +5617,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>5056000</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>27628</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4347,6 +5679,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>5226000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>28097</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4393,6 +5741,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>6976530</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>26426</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4439,6 +5803,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>6517170</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>26930</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4485,6 +5865,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>4730080</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>25431</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4531,6 +5927,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>4672740</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>25534</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4577,6 +5989,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>4774700</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>26091</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4623,6 +6051,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>4934300</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>26528</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4669,6 +6113,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>6631000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>27401</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4715,6 +6175,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>6474600</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>26755</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4761,6 +6237,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>4678380</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>25153</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4807,6 +6299,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>4644540</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>25380</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4853,6 +6361,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>4696240</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>25663</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4899,6 +6423,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>4852280</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>26088</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4945,6 +6485,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>6360040</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>26281</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4991,6 +6547,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>6107180</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>25236</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5037,6 +6609,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>4697180</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>25254</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5083,6 +6671,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>4847040</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>26487</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5129,6 +6733,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>4704400</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>25707</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5175,6 +6795,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>4807160</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>25845</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5221,6 +6857,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>6387800</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>26396</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5267,6 +6919,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>6390450</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>26407</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5313,6 +6981,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>4608820</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>24779</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5359,6 +7043,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>4788630</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>26167</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5405,6 +7105,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>4647400</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>25396</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5451,6 +7167,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>4747000</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>25522</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5497,6 +7229,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>6260400</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>25869</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5543,6 +7291,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>6347880</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>26231</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5589,6 +7353,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>4626680</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>24875</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5635,6 +7415,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>4504480</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>24615</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5681,6 +7477,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>4556180</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>24897</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5727,6 +7539,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>4702820</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>25284</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5773,6 +7601,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>6376020</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>26347</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5819,6 +7663,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>6007540</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>24825</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5865,6 +7725,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>4569340</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>24566</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5911,6 +7787,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>4490380</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>24538</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5957,6 +7849,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>4542080</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>24820</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6003,6 +7911,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>4937130</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>26544</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6049,6 +7973,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>6355340</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>26262</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6095,6 +8035,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>5963360</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>24642</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6141,6 +8097,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>4503950</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>24215</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6187,6 +8159,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>4509650</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>24643</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6233,6 +8221,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>4514820</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>24671</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6279,6 +8283,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>4707250</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>25308</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6325,6 +8345,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>6226300</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>25729</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6371,6 +8407,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>5923880</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>24479</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6417,6 +8469,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>4643100</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>24963</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6463,6 +8531,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>4434920</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>24235</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6509,6 +8593,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>4725270</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>25821</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6559,6 +8659,26 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6605,6 +8725,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>6120340</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>25291</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6651,6 +8787,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>5926100</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>24488</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6697,6 +8849,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>4437450</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>23857</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6743,6 +8911,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>4392620</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>24003</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6789,6 +8973,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>4444320</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>24286</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6835,6 +9035,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>4582500</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>24637</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>現金或即時按揭付款計劃 - 210天成交</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6881,6 +9097,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>6123700</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>25305</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6927,6 +9159,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>5807320</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>23997</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6973,6 +9221,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>4276060</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>22990</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7019,6 +9283,22 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>4382350</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>23947</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7065,6 +9345,22 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>4388860</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>23983</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7111,6 +9407,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>4522340</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>24314</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7157,13 +9469,29 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>5998140</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>24786</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -7375,7 +9703,7 @@
           <t>A | 264呎 (1房)
 $736万
 $27,897/呎
-(23年-03月)</t>
+(23年-03月-28日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -7415,7 +9743,7 @@
           <t>F | 264呎 (1房)
 $716万
 $27,125/呎
-(23年-03月)</t>
+(23年-03月-30日)</t>
         </is>
       </c>
     </row>
@@ -7430,7 +9758,7 @@
           <t>A | 264呎 (1房)
 $726万
 $27,506/呎
-(21年-11月)</t>
+(21年-11月-09日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -7485,7 +9813,7 @@
           <t>A | 264呎 (1房)
 $720万
 $27,274/呎
-(23年-05月)</t>
+(23年-05月-07日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -7540,7 +9868,7 @@
           <t>A | 264呎 (1房)
 $714万
 $27,039/呎
-(21年-08月)</t>
+(21年-08月-16日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -7548,7 +9876,7 @@
           <t>B | 186呎 (开放式)
 $515万
 $27,700/呎
-(21年-09月)</t>
+(21年-09月-22日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -7564,7 +9892,7 @@
           <t>D | 183呎 (开放式)
 $492万
 $26,910/呎
-(23年-04月)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -7580,7 +9908,7 @@
           <t>F | 264呎 (1房)
 $672万
 $25,451/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -7595,7 +9923,7 @@
           <t>A | 264呎 (1房)
 $708万
 $26,808/呎
-(21年-06月)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -7603,7 +9931,7 @@
           <t>B | 186呎 (开放式)
 $512万
 $27,538/呎
-(22年-02月)</t>
+(22年-02月-21日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -7650,7 +9978,7 @@
           <t>A | 264呎 (1房)
 $704万
 $26,655/呎
-(21年-07月)</t>
+(21年-07月-01日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -7658,7 +9986,7 @@
           <t>B | 186呎 (开放式)
 $509万
 $27,381/呎
-(21年-06月)</t>
+(21年-06月-23日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -7682,7 +10010,7 @@
           <t>E | 186呎 (开放式)
 $493万
 $26,492/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -7690,7 +10018,7 @@
           <t>F | 264呎 (1房)
 $662万
 $25,092/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -7705,7 +10033,7 @@
           <t>A | 264呎 (1房)
 $707万
 $26,780/呎
-(21年-09月)</t>
+(21年-09月-22日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -7713,7 +10041,7 @@
           <t>B | 186呎 (开放式)
 $539万
 $28,957/呎
-(21年-08月)</t>
+(21年-08月-16日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -7745,7 +10073,7 @@
           <t>F | 264呎 (1房)
 $666万
 $25,215/呎
-(21年-06月)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -7760,7 +10088,7 @@
           <t>A | 264呎 (1房)
 $678万
 $25,700/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -7768,7 +10096,7 @@
           <t>B | 186呎 (开放式)
 $530万
 $28,497/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -7776,7 +10104,7 @@
           <t>C | 183呎 (开放式)
 $486万
 $26,582/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -7792,7 +10120,7 @@
           <t>E | 186呎 (开放式)
 $487万
 $26,184/呎
-(21年-06月)</t>
+(21年-06月-24日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -7800,7 +10128,7 @@
           <t>F | 264呎 (1房)
 $655万
 $24,803/呎
-(21年-06月)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -7815,7 +10143,7 @@
           <t>A | 264呎 (1房)
 $728万
 $27,585/呎
-(21年-06月)</t>
+(21年-06月-24日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -7823,7 +10151,7 @@
           <t>B | 186呎 (开放式)
 $506万
 $27,182/呎
-(21年-12月)</t>
+(21年-12月-19日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -7847,7 +10175,7 @@
           <t>E | 186呎 (开放式)
 $484万
 $26,037/呎
-(22年-07月)</t>
+(22年-07月-11日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -7855,7 +10183,7 @@
           <t>F | 264呎 (1房)
 $675万
 $25,567/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -7870,7 +10198,7 @@
           <t>A | 264呎 (1房)
 $687万
 $26,035/呎
-(21年-06月)</t>
+(21年-06月-20日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -7878,7 +10206,7 @@
           <t>B | 186呎 (开放式)
 $497万
 $26,734/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -7910,7 +10238,7 @@
           <t>F | 264呎 (1房)
 $655万
 $24,808/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -7925,7 +10253,7 @@
           <t>A | 264呎 (1房)
 $666万
 $25,245/呎
-(21年-06月)</t>
+(21年-06月-20日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -7933,7 +10261,7 @@
           <t>B | 186呎 (开放式)
 $500万
 $26,855/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -7941,7 +10269,7 @@
           <t>C | 183呎 (开放式)
 $504万
 $27,514/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -7949,7 +10277,7 @@
           <t>D | 183呎 (开放式)
 $473万
 $25,837/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -7965,7 +10293,7 @@
           <t>F | 264呎 (1房)
 $667万
 $25,279/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -7980,7 +10308,7 @@
           <t>A | 264呎 (1房)
 $698万
 $26,426/呎
-(21年-06月)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -7988,7 +10316,7 @@
           <t>B | 186呎 (开放式)
 $523万
 $28,097/呎
-(21年-06月)</t>
+(21年-06月-20日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -7996,7 +10324,7 @@
           <t>C | 183呎 (开放式)
 $506万
 $27,628/呎
-(21年-12月)</t>
+(21年-12月-28日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -8004,7 +10332,7 @@
           <t>D | 183呎 (开放式)
 $470万
 $25,683/呎
-(21年-06月)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -8012,7 +10340,7 @@
           <t>E | 186呎 (开放式)
 $476万
 $25,582/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -8035,7 +10363,7 @@
           <t>A | 242呎 (1房)
 $663万
 $27,401/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -8043,7 +10371,7 @@
           <t>B | 186呎 (开放式)
 $493万
 $26,528/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -8051,7 +10379,7 @@
           <t>C | 183呎 (开放式)
 $477万
 $26,091/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -8059,7 +10387,7 @@
           <t>D | 183呎 (开放式)
 $467万
 $25,534/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -8067,7 +10395,7 @@
           <t>E | 186呎 (开放式)
 $473万
 $25,431/呎
-(22年-08月)</t>
+(22年-08月-04日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -8075,7 +10403,7 @@
           <t>F | 242呎 (1房)
 $652万
 $26,930/呎
-(21年-06月)</t>
+(21年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -8090,7 +10418,7 @@
           <t>A | 242呎 (1房)
 $636万
 $26,281/呎
-(21年-06月)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -8098,7 +10426,7 @@
           <t>B | 186呎 (开放式)
 $485万
 $26,088/呎
-(21年-08月)</t>
+(21年-08月-08日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -8106,7 +10434,7 @@
           <t>C | 183呎 (开放式)
 $470万
 $25,663/呎
-(21年-06月)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -8114,7 +10442,7 @@
           <t>D | 183呎 (开放式)
 $464万
 $25,380/呎
-(21年-06月)</t>
+(21年-06月-27日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -8122,7 +10450,7 @@
           <t>E | 186呎 (开放式)
 $468万
 $25,153/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -8130,7 +10458,7 @@
           <t>F | 242呎 (1房)
 $647万
 $26,755/呎
-(21年-06月)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -8145,7 +10473,7 @@
           <t>A | 242呎 (1房)
 $639万
 $26,396/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -8153,7 +10481,7 @@
           <t>B | 186呎 (开放式)
 $481万
 $25,845/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -8161,7 +10489,7 @@
           <t>C | 183呎 (开放式)
 $470万
 $25,707/呎
-(21年-08月)</t>
+(21年-08月-17日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -8169,7 +10497,7 @@
           <t>D | 183呎 (开放式)
 $485万
 $26,487/呎
-(21年-08月)</t>
+(21年-08月-11日)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -8185,7 +10513,7 @@
           <t>F | 242呎 (1房)
 $611万
 $25,236/呎
-(21年-06月)</t>
+(21年-06月-20日)</t>
         </is>
       </c>
     </row>
@@ -8200,7 +10528,7 @@
           <t>A | 242呎 (1房)
 $626万
 $25,869/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -8208,7 +10536,7 @@
           <t>B | 186呎 (开放式)
 $475万
 $25,522/呎
-(21年-06月)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -8216,7 +10544,7 @@
           <t>C | 183呎 (开放式)
 $465万
 $25,396/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -8224,7 +10552,7 @@
           <t>D | 183呎 (开放式)
 $479万
 $26,167/呎
-(21年-06月)</t>
+(21年-06月-27日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -8232,7 +10560,7 @@
           <t>E | 186呎 (开放式)
 $461万
 $24,779/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -8240,7 +10568,7 @@
           <t>F | 242呎 (1房)
 $639万
 $26,407/呎
-(21年-06月)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -8255,7 +10583,7 @@
           <t>A | 242呎 (1房)
 $638万
 $26,347/呎
-(21年-12月)</t>
+(21年-12月-23日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -8263,7 +10591,7 @@
           <t>B | 186呎 (开放式)
 $470万
 $25,284/呎
-(21年-10月)</t>
+(21年-10月-19日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -8271,7 +10599,7 @@
           <t>C | 183呎 (开放式)
 $456万
 $24,897/呎
-(21年-10月)</t>
+(21年-10月-26日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -8295,7 +10623,7 @@
           <t>F | 242呎 (1房)
 $635万
 $26,231/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -8310,7 +10638,7 @@
           <t>A | 242呎 (1房)
 $636万
 $26,262/呎
-(22年-02月)</t>
+(22年-02月-23日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -8318,7 +10646,7 @@
           <t>B | 186呎 (开放式)
 $494万
 $26,544/呎
-(21年-11月)</t>
+(21年-11月-25日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -8350,7 +10678,7 @@
           <t>F | 242呎 (1房)
 $601万
 $24,825/呎
-(21年-06月)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -8365,7 +10693,7 @@
           <t>A | 242呎 (1房)
 $623万
 $25,729/呎
-(21年-06月)</t>
+(21年-06月-20日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -8373,7 +10701,7 @@
           <t>B | 186呎 (开放式)
 $471万
 $25,308/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -8381,7 +10709,7 @@
           <t>C | 183呎 (开放式)
 $451万
 $24,671/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -8389,7 +10717,7 @@
           <t>D | 183呎 (开放式)
 $451万
 $24,643/呎
-(21年-06月)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -8397,7 +10725,7 @@
           <t>E | 186呎 (开放式)
 $450万
 $24,215/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -8405,7 +10733,7 @@
           <t>F | 242呎 (1房)
 $596万
 $24,642/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -8420,7 +10748,7 @@
           <t>A | 242呎 (1房)
 $612万
 $25,291/呎
-(21年-06月)</t>
+(21年-06月-20日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -8436,7 +10764,7 @@
           <t>C | 183呎 (开放式)
 $473万
 $25,821/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -8444,7 +10772,7 @@
           <t>D | 183呎 (开放式)
 $443万
 $24,235/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -8452,7 +10780,7 @@
           <t>E | 186呎 (开放式)
 $464万
 $24,963/呎
-(21年-06月)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -8460,7 +10788,7 @@
           <t>F | 242呎 (1房)
 $592万
 $24,479/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -8475,7 +10803,7 @@
           <t>A | 242呎 (1房)
 $612万
 $25,305/呎
-(21年-07月)</t>
+(21年-07月-01日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -8491,7 +10819,7 @@
           <t>C | 183呎 (开放式)
 $444万
 $24,286/呎
-(21年-08月)</t>
+(21年-08月-16日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -8499,7 +10827,7 @@
           <t>D | 183呎 (开放式)
 $439万
 $24,003/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -8507,7 +10835,7 @@
           <t>E | 186呎 (开放式)
 $444万
 $23,857/呎
-(21年-09月)</t>
+(21年-09月-22日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -8515,7 +10843,7 @@
           <t>F | 242呎 (1房)
 $593万
 $24,488/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -8530,7 +10858,7 @@
           <t>A | 242呎 (1房)
 $600万
 $24,786/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -8538,7 +10866,7 @@
           <t>B | 186呎 (开放式)
 $452万
 $24,314/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -8546,7 +10874,7 @@
           <t>C | 183呎 (开放式)
 $439万
 $23,983/呎
-(21年-06月)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -8554,7 +10882,7 @@
           <t>D | 183呎 (开放式)
 $438万
 $23,947/呎
-(21年-11月)</t>
+(21年-11月-11日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -8562,7 +10890,7 @@
           <t>E | 186呎 (开放式)
 $428万
 $22,990/呎
-(21年-05月)</t>
+(21年-05月-29日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -8570,7 +10898,7 @@
           <t>F | 242呎 (1房)
 $581万
 $23,997/呎
-(21年-06月)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-逸南.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-逸南.xlsx
@@ -9703,7 +9703,7 @@
           <t>A | 264呎 (1房)
 $736万
 $27,897/呎
-(23年-03月-28日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -9743,7 +9743,7 @@
           <t>F | 264呎 (1房)
 $716万
 $27,125/呎
-(23年-03月-30日)</t>
+(23年-03月)</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9758,7 @@
           <t>A | 264呎 (1房)
 $726万
 $27,506/呎
-(21年-11月-09日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -9813,7 +9813,7 @@
           <t>A | 264呎 (1房)
 $720万
 $27,274/呎
-(23年-05月-07日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -9868,7 +9868,7 @@
           <t>A | 264呎 (1房)
 $714万
 $27,039/呎
-(21年-08月-16日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -9876,7 +9876,7 @@
           <t>B | 186呎 (开放式)
 $515万
 $27,700/呎
-(21年-09月-22日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -9892,7 +9892,7 @@
           <t>D | 183呎 (开放式)
 $492万
 $26,910/呎
-(23年-04月-27日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -9908,7 +9908,7 @@
           <t>F | 264呎 (1房)
 $672万
 $25,451/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
           <t>A | 264呎 (1房)
 $708万
 $26,808/呎
-(21年-06月-29日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -9931,7 +9931,7 @@
           <t>B | 186呎 (开放式)
 $512万
 $27,538/呎
-(22年-02月-21日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -9978,7 +9978,7 @@
           <t>A | 264呎 (1房)
 $704万
 $26,655/呎
-(21年-07月-01日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -9986,7 +9986,7 @@
           <t>B | 186呎 (开放式)
 $509万
 $27,381/呎
-(21年-06月-23日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -10010,7 +10010,7 @@
           <t>E | 186呎 (开放式)
 $493万
 $26,492/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -10018,7 +10018,7 @@
           <t>F | 264呎 (1房)
 $662万
 $25,092/呎
-(21年-06月-21日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
           <t>A | 264呎 (1房)
 $707万
 $26,780/呎
-(21年-09月-22日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -10041,7 +10041,7 @@
           <t>B | 186呎 (开放式)
 $539万
 $28,957/呎
-(21年-08月-16日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -10073,7 +10073,7 @@
           <t>F | 264呎 (1房)
 $666万
 $25,215/呎
-(21年-06月-15日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10088,7 @@
           <t>A | 264呎 (1房)
 $678万
 $25,700/呎
-(21年-06月-22日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -10096,7 +10096,7 @@
           <t>B | 186呎 (开放式)
 $530万
 $28,497/呎
-(21年-06月-22日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -10104,7 +10104,7 @@
           <t>C | 183呎 (开放式)
 $486万
 $26,582/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -10120,7 +10120,7 @@
           <t>E | 186呎 (开放式)
 $487万
 $26,184/呎
-(21年-06月-24日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -10128,7 +10128,7 @@
           <t>F | 264呎 (1房)
 $655万
 $24,803/呎
-(21年-06月-28日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
           <t>A | 264呎 (1房)
 $728万
 $27,585/呎
-(21年-06月-24日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -10151,7 +10151,7 @@
           <t>B | 186呎 (开放式)
 $506万
 $27,182/呎
-(21年-12月-19日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -10175,7 +10175,7 @@
           <t>E | 186呎 (开放式)
 $484万
 $26,037/呎
-(22年-07月-11日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -10183,7 +10183,7 @@
           <t>F | 264呎 (1房)
 $675万
 $25,567/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -10198,7 +10198,7 @@
           <t>A | 264呎 (1房)
 $687万
 $26,035/呎
-(21年-06月-20日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -10206,7 +10206,7 @@
           <t>B | 186呎 (开放式)
 $497万
 $26,734/呎
-(22年-01月-06日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -10238,7 +10238,7 @@
           <t>F | 264呎 (1房)
 $655万
 $24,808/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -10253,7 +10253,7 @@
           <t>A | 264呎 (1房)
 $666万
 $25,245/呎
-(21年-06月-20日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -10261,7 +10261,7 @@
           <t>B | 186呎 (开放式)
 $500万
 $26,855/呎
-(21年-06月-21日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -10269,7 +10269,7 @@
           <t>C | 183呎 (开放式)
 $504万
 $27,514/呎
-(21年-06月-22日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -10277,7 +10277,7 @@
           <t>D | 183呎 (开放式)
 $473万
 $25,837/呎
-(21年-06月-21日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -10293,7 +10293,7 @@
           <t>F | 264呎 (1房)
 $667万
 $25,279/呎
-(21年-07月-12日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10308,7 @@
           <t>A | 264呎 (1房)
 $698万
 $26,426/呎
-(21年-06月-17日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -10316,7 +10316,7 @@
           <t>B | 186呎 (开放式)
 $523万
 $28,097/呎
-(21年-06月-20日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -10324,7 +10324,7 @@
           <t>C | 183呎 (开放式)
 $506万
 $27,628/呎
-(21年-12月-28日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -10332,7 +10332,7 @@
           <t>D | 183呎 (开放式)
 $470万
 $25,683/呎
-(21年-06月-29日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -10340,7 +10340,7 @@
           <t>E | 186呎 (开放式)
 $476万
 $25,582/呎
-(21年-06月-21日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -10363,7 +10363,7 @@
           <t>A | 242呎 (1房)
 $663万
 $27,401/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -10371,7 +10371,7 @@
           <t>B | 186呎 (开放式)
 $493万
 $26,528/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -10379,7 +10379,7 @@
           <t>C | 183呎 (开放式)
 $477万
 $26,091/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -10387,7 +10387,7 @@
           <t>D | 183呎 (开放式)
 $467万
 $25,534/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -10395,7 +10395,7 @@
           <t>E | 186呎 (开放式)
 $473万
 $25,431/呎
-(22年-08月-04日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -10403,7 +10403,7 @@
           <t>F | 242呎 (1房)
 $652万
 $26,930/呎
-(21年-06月-23日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -10418,7 +10418,7 @@
           <t>A | 242呎 (1房)
 $636万
 $26,281/呎
-(21年-06月-15日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -10426,7 +10426,7 @@
           <t>B | 186呎 (开放式)
 $485万
 $26,088/呎
-(21年-08月-08日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -10434,7 +10434,7 @@
           <t>C | 183呎 (开放式)
 $470万
 $25,663/呎
-(21年-06月-15日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -10442,7 +10442,7 @@
           <t>D | 183呎 (开放式)
 $464万
 $25,380/呎
-(21年-06月-27日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -10450,7 +10450,7 @@
           <t>E | 186呎 (开放式)
 $468万
 $25,153/呎
-(21年-06月-21日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -10458,7 +10458,7 @@
           <t>F | 242呎 (1房)
 $647万
 $26,755/呎
-(21年-06月-16日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -10473,7 +10473,7 @@
           <t>A | 242呎 (1房)
 $639万
 $26,396/呎
-(21年-06月-21日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -10481,7 +10481,7 @@
           <t>B | 186呎 (开放式)
 $481万
 $25,845/呎
-(21年-10月-07日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -10489,7 +10489,7 @@
           <t>C | 183呎 (开放式)
 $470万
 $25,707/呎
-(21年-08月-17日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -10497,7 +10497,7 @@
           <t>D | 183呎 (开放式)
 $485万
 $26,487/呎
-(21年-08月-11日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -10513,7 +10513,7 @@
           <t>F | 242呎 (1房)
 $611万
 $25,236/呎
-(21年-06月-20日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -10528,7 +10528,7 @@
           <t>A | 242呎 (1房)
 $626万
 $25,869/呎
-(21年-06月-21日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -10536,7 +10536,7 @@
           <t>B | 186呎 (开放式)
 $475万
 $25,522/呎
-(21年-06月-28日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -10544,7 +10544,7 @@
           <t>C | 183呎 (开放式)
 $465万
 $25,396/呎
-(21年-06月-21日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -10552,7 +10552,7 @@
           <t>D | 183呎 (开放式)
 $479万
 $26,167/呎
-(21年-06月-27日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -10560,7 +10560,7 @@
           <t>E | 186呎 (开放式)
 $461万
 $24,779/呎
-(21年-06月-21日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -10568,7 +10568,7 @@
           <t>F | 242呎 (1房)
 $639万
 $26,407/呎
-(21年-06月-28日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -10583,7 +10583,7 @@
           <t>A | 242呎 (1房)
 $638万
 $26,347/呎
-(21年-12月-23日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -10591,7 +10591,7 @@
           <t>B | 186呎 (开放式)
 $470万
 $25,284/呎
-(21年-10月-19日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -10599,7 +10599,7 @@
           <t>C | 183呎 (开放式)
 $456万
 $24,897/呎
-(21年-10月-26日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -10623,7 +10623,7 @@
           <t>F | 242呎 (1房)
 $635万
 $26,231/呎
-(21年-06月-21日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -10638,7 +10638,7 @@
           <t>A | 242呎 (1房)
 $636万
 $26,262/呎
-(22年-02月-23日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -10646,7 +10646,7 @@
           <t>B | 186呎 (开放式)
 $494万
 $26,544/呎
-(21年-11月-25日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -10678,7 +10678,7 @@
           <t>F | 242呎 (1房)
 $601万
 $24,825/呎
-(21年-06月-28日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -10693,7 +10693,7 @@
           <t>A | 242呎 (1房)
 $623万
 $25,729/呎
-(21年-06月-20日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -10701,7 +10701,7 @@
           <t>B | 186呎 (开放式)
 $471万
 $25,308/呎
-(21年-06月-21日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -10709,7 +10709,7 @@
           <t>C | 183呎 (开放式)
 $451万
 $24,671/呎
-(21年-06月-22日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -10717,7 +10717,7 @@
           <t>D | 183呎 (开放式)
 $451万
 $24,643/呎
-(21年-06月-28日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -10725,7 +10725,7 @@
           <t>E | 186呎 (开放式)
 $450万
 $24,215/呎
-(21年-06月-22日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -10733,7 +10733,7 @@
           <t>F | 242呎 (1房)
 $596万
 $24,642/呎
-(21年-06月-22日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10748,7 @@
           <t>A | 242呎 (1房)
 $612万
 $25,291/呎
-(21年-06月-20日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -10764,7 +10764,7 @@
           <t>C | 183呎 (开放式)
 $473万
 $25,821/呎
-(21年-06月-21日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -10772,7 +10772,7 @@
           <t>D | 183呎 (开放式)
 $443万
 $24,235/呎
-(21年-06月-22日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -10780,7 +10780,7 @@
           <t>E | 186呎 (开放式)
 $464万
 $24,963/呎
-(21年-06月-15日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -10788,7 +10788,7 @@
           <t>F | 242呎 (1房)
 $592万
 $24,479/呎
-(21年-06月-21日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10803,7 @@
           <t>A | 242呎 (1房)
 $612万
 $25,305/呎
-(21年-07月-01日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -10819,7 +10819,7 @@
           <t>C | 183呎 (开放式)
 $444万
 $24,286/呎
-(21年-08月-16日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -10827,7 +10827,7 @@
           <t>D | 183呎 (开放式)
 $439万
 $24,003/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -10835,7 +10835,7 @@
           <t>E | 186呎 (开放式)
 $444万
 $23,857/呎
-(21年-09月-22日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -10843,7 +10843,7 @@
           <t>F | 242呎 (1房)
 $593万
 $24,488/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -10858,7 +10858,7 @@
           <t>A | 242呎 (1房)
 $600万
 $24,786/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -10866,7 +10866,7 @@
           <t>B | 186呎 (开放式)
 $452万
 $24,314/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -10874,7 +10874,7 @@
           <t>C | 183呎 (开放式)
 $439万
 $23,983/呎
-(21年-06月-16日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -10882,7 +10882,7 @@
           <t>D | 183呎 (开放式)
 $438万
 $23,947/呎
-(21年-11月-11日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -10890,7 +10890,7 @@
           <t>E | 186呎 (开放式)
 $428万
 $22,990/呎
-(21年-05月-29日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -10898,7 +10898,7 @@
           <t>F | 242呎 (1房)
 $581万
 $23,997/呎
-(21年-06月-10日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-逸南.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-逸南.xlsx
@@ -9703,7 +9703,7 @@
           <t>A | 264呎 (1房)
 $736万
 $27,897/呎
-(23年-03月)</t>
+(23年-03月-28日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -9743,7 +9743,7 @@
           <t>F | 264呎 (1房)
 $716万
 $27,125/呎
-(23年-03月)</t>
+(23年-03月-30日)</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9758,7 @@
           <t>A | 264呎 (1房)
 $726万
 $27,506/呎
-(21年-11月)</t>
+(21年-11月-09日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -9813,7 +9813,7 @@
           <t>A | 264呎 (1房)
 $720万
 $27,274/呎
-(23年-05月)</t>
+(23年-05月-07日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -9868,7 +9868,7 @@
           <t>A | 264呎 (1房)
 $714万
 $27,039/呎
-(21年-08月)</t>
+(21年-08月-16日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -9876,7 +9876,7 @@
           <t>B | 186呎 (开放式)
 $515万
 $27,700/呎
-(21年-09月)</t>
+(21年-09月-22日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -9892,7 +9892,7 @@
           <t>D | 183呎 (开放式)
 $492万
 $26,910/呎
-(23年-04月)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -9908,7 +9908,7 @@
           <t>F | 264呎 (1房)
 $672万
 $25,451/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
           <t>A | 264呎 (1房)
 $708万
 $26,808/呎
-(21年-06月)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -9931,7 +9931,7 @@
           <t>B | 186呎 (开放式)
 $512万
 $27,538/呎
-(22年-02月)</t>
+(22年-02月-21日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -9978,7 +9978,7 @@
           <t>A | 264呎 (1房)
 $704万
 $26,655/呎
-(21年-07月)</t>
+(21年-07月-01日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -9986,7 +9986,7 @@
           <t>B | 186呎 (开放式)
 $509万
 $27,381/呎
-(21年-06月)</t>
+(21年-06月-23日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -10010,7 +10010,7 @@
           <t>E | 186呎 (开放式)
 $493万
 $26,492/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -10018,7 +10018,7 @@
           <t>F | 264呎 (1房)
 $662万
 $25,092/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
           <t>A | 264呎 (1房)
 $707万
 $26,780/呎
-(21年-09月)</t>
+(21年-09月-22日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -10041,7 +10041,7 @@
           <t>B | 186呎 (开放式)
 $539万
 $28,957/呎
-(21年-08月)</t>
+(21年-08月-16日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -10073,7 +10073,7 @@
           <t>F | 264呎 (1房)
 $666万
 $25,215/呎
-(21年-06月)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10088,7 @@
           <t>A | 264呎 (1房)
 $678万
 $25,700/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -10096,7 +10096,7 @@
           <t>B | 186呎 (开放式)
 $530万
 $28,497/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -10104,7 +10104,7 @@
           <t>C | 183呎 (开放式)
 $486万
 $26,582/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -10120,7 +10120,7 @@
           <t>E | 186呎 (开放式)
 $487万
 $26,184/呎
-(21年-06月)</t>
+(21年-06月-24日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -10128,7 +10128,7 @@
           <t>F | 264呎 (1房)
 $655万
 $24,803/呎
-(21年-06月)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
           <t>A | 264呎 (1房)
 $728万
 $27,585/呎
-(21年-06月)</t>
+(21年-06月-24日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -10151,7 +10151,7 @@
           <t>B | 186呎 (开放式)
 $506万
 $27,182/呎
-(21年-12月)</t>
+(21年-12月-19日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -10175,7 +10175,7 @@
           <t>E | 186呎 (开放式)
 $484万
 $26,037/呎
-(22年-07月)</t>
+(22年-07月-11日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -10183,7 +10183,7 @@
           <t>F | 264呎 (1房)
 $675万
 $25,567/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -10198,7 +10198,7 @@
           <t>A | 264呎 (1房)
 $687万
 $26,035/呎
-(21年-06月)</t>
+(21年-06月-20日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -10206,7 +10206,7 @@
           <t>B | 186呎 (开放式)
 $497万
 $26,734/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -10238,7 +10238,7 @@
           <t>F | 264呎 (1房)
 $655万
 $24,808/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -10253,7 +10253,7 @@
           <t>A | 264呎 (1房)
 $666万
 $25,245/呎
-(21年-06月)</t>
+(21年-06月-20日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -10261,7 +10261,7 @@
           <t>B | 186呎 (开放式)
 $500万
 $26,855/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -10269,7 +10269,7 @@
           <t>C | 183呎 (开放式)
 $504万
 $27,514/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -10277,7 +10277,7 @@
           <t>D | 183呎 (开放式)
 $473万
 $25,837/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -10293,7 +10293,7 @@
           <t>F | 264呎 (1房)
 $667万
 $25,279/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10308,7 @@
           <t>A | 264呎 (1房)
 $698万
 $26,426/呎
-(21年-06月)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -10316,7 +10316,7 @@
           <t>B | 186呎 (开放式)
 $523万
 $28,097/呎
-(21年-06月)</t>
+(21年-06月-20日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -10324,7 +10324,7 @@
           <t>C | 183呎 (开放式)
 $506万
 $27,628/呎
-(21年-12月)</t>
+(21年-12月-28日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -10332,7 +10332,7 @@
           <t>D | 183呎 (开放式)
 $470万
 $25,683/呎
-(21年-06月)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -10340,7 +10340,7 @@
           <t>E | 186呎 (开放式)
 $476万
 $25,582/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -10363,7 +10363,7 @@
           <t>A | 242呎 (1房)
 $663万
 $27,401/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -10371,7 +10371,7 @@
           <t>B | 186呎 (开放式)
 $493万
 $26,528/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -10379,7 +10379,7 @@
           <t>C | 183呎 (开放式)
 $477万
 $26,091/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -10387,7 +10387,7 @@
           <t>D | 183呎 (开放式)
 $467万
 $25,534/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -10395,7 +10395,7 @@
           <t>E | 186呎 (开放式)
 $473万
 $25,431/呎
-(22年-08月)</t>
+(22年-08月-04日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -10403,7 +10403,7 @@
           <t>F | 242呎 (1房)
 $652万
 $26,930/呎
-(21年-06月)</t>
+(21年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -10418,7 +10418,7 @@
           <t>A | 242呎 (1房)
 $636万
 $26,281/呎
-(21年-06月)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -10426,7 +10426,7 @@
           <t>B | 186呎 (开放式)
 $485万
 $26,088/呎
-(21年-08月)</t>
+(21年-08月-08日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -10434,7 +10434,7 @@
           <t>C | 183呎 (开放式)
 $470万
 $25,663/呎
-(21年-06月)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -10442,7 +10442,7 @@
           <t>D | 183呎 (开放式)
 $464万
 $25,380/呎
-(21年-06月)</t>
+(21年-06月-27日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -10450,7 +10450,7 @@
           <t>E | 186呎 (开放式)
 $468万
 $25,153/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -10458,7 +10458,7 @@
           <t>F | 242呎 (1房)
 $647万
 $26,755/呎
-(21年-06月)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -10473,7 +10473,7 @@
           <t>A | 242呎 (1房)
 $639万
 $26,396/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -10481,7 +10481,7 @@
           <t>B | 186呎 (开放式)
 $481万
 $25,845/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -10489,7 +10489,7 @@
           <t>C | 183呎 (开放式)
 $470万
 $25,707/呎
-(21年-08月)</t>
+(21年-08月-17日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -10497,7 +10497,7 @@
           <t>D | 183呎 (开放式)
 $485万
 $26,487/呎
-(21年-08月)</t>
+(21年-08月-11日)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -10513,7 +10513,7 @@
           <t>F | 242呎 (1房)
 $611万
 $25,236/呎
-(21年-06月)</t>
+(21年-06月-20日)</t>
         </is>
       </c>
     </row>
@@ -10528,7 +10528,7 @@
           <t>A | 242呎 (1房)
 $626万
 $25,869/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -10536,7 +10536,7 @@
           <t>B | 186呎 (开放式)
 $475万
 $25,522/呎
-(21年-06月)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -10544,7 +10544,7 @@
           <t>C | 183呎 (开放式)
 $465万
 $25,396/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -10552,7 +10552,7 @@
           <t>D | 183呎 (开放式)
 $479万
 $26,167/呎
-(21年-06月)</t>
+(21年-06月-27日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -10560,7 +10560,7 @@
           <t>E | 186呎 (开放式)
 $461万
 $24,779/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -10568,7 +10568,7 @@
           <t>F | 242呎 (1房)
 $639万
 $26,407/呎
-(21年-06月)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -10583,7 +10583,7 @@
           <t>A | 242呎 (1房)
 $638万
 $26,347/呎
-(21年-12月)</t>
+(21年-12月-23日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -10591,7 +10591,7 @@
           <t>B | 186呎 (开放式)
 $470万
 $25,284/呎
-(21年-10月)</t>
+(21年-10月-19日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -10599,7 +10599,7 @@
           <t>C | 183呎 (开放式)
 $456万
 $24,897/呎
-(21年-10月)</t>
+(21年-10月-26日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -10623,7 +10623,7 @@
           <t>F | 242呎 (1房)
 $635万
 $26,231/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -10638,7 +10638,7 @@
           <t>A | 242呎 (1房)
 $636万
 $26,262/呎
-(22年-02月)</t>
+(22年-02月-23日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -10646,7 +10646,7 @@
           <t>B | 186呎 (开放式)
 $494万
 $26,544/呎
-(21年-11月)</t>
+(21年-11月-25日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -10678,7 +10678,7 @@
           <t>F | 242呎 (1房)
 $601万
 $24,825/呎
-(21年-06月)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -10693,7 +10693,7 @@
           <t>A | 242呎 (1房)
 $623万
 $25,729/呎
-(21年-06月)</t>
+(21年-06月-20日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -10701,7 +10701,7 @@
           <t>B | 186呎 (开放式)
 $471万
 $25,308/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -10709,7 +10709,7 @@
           <t>C | 183呎 (开放式)
 $451万
 $24,671/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -10717,7 +10717,7 @@
           <t>D | 183呎 (开放式)
 $451万
 $24,643/呎
-(21年-06月)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -10725,7 +10725,7 @@
           <t>E | 186呎 (开放式)
 $450万
 $24,215/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -10733,7 +10733,7 @@
           <t>F | 242呎 (1房)
 $596万
 $24,642/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10748,7 @@
           <t>A | 242呎 (1房)
 $612万
 $25,291/呎
-(21年-06月)</t>
+(21年-06月-20日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -10764,7 +10764,7 @@
           <t>C | 183呎 (开放式)
 $473万
 $25,821/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -10772,7 +10772,7 @@
           <t>D | 183呎 (开放式)
 $443万
 $24,235/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -10780,7 +10780,7 @@
           <t>E | 186呎 (开放式)
 $464万
 $24,963/呎
-(21年-06月)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -10788,7 +10788,7 @@
           <t>F | 242呎 (1房)
 $592万
 $24,479/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10803,7 @@
           <t>A | 242呎 (1房)
 $612万
 $25,305/呎
-(21年-07月)</t>
+(21年-07月-01日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -10819,7 +10819,7 @@
           <t>C | 183呎 (开放式)
 $444万
 $24,286/呎
-(21年-08月)</t>
+(21年-08月-16日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -10827,7 +10827,7 @@
           <t>D | 183呎 (开放式)
 $439万
 $24,003/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -10835,7 +10835,7 @@
           <t>E | 186呎 (开放式)
 $444万
 $23,857/呎
-(21年-09月)</t>
+(21年-09月-22日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -10843,7 +10843,7 @@
           <t>F | 242呎 (1房)
 $593万
 $24,488/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -10858,7 +10858,7 @@
           <t>A | 242呎 (1房)
 $600万
 $24,786/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -10866,7 +10866,7 @@
           <t>B | 186呎 (开放式)
 $452万
 $24,314/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -10874,7 +10874,7 @@
           <t>C | 183呎 (开放式)
 $439万
 $23,983/呎
-(21年-06月)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -10882,7 +10882,7 @@
           <t>D | 183呎 (开放式)
 $438万
 $23,947/呎
-(21年-11月)</t>
+(21年-11月-11日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -10890,7 +10890,7 @@
           <t>E | 186呎 (开放式)
 $428万
 $22,990/呎
-(21年-05月)</t>
+(21年-05月-29日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -10898,7 +10898,7 @@
           <t>F | 242呎 (1房)
 $581万
 $23,997/呎
-(21年-06月)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
     </row>
